--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -939,11 +939,11 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
@@ -964,13 +964,13 @@
         <v>-50</v>
       </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M16" s="14">
         <v>0</v>
       </c>
       <c r="N16" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F17" s="15">
+        <v>8</v>
+      </c>
+      <c r="G17" s="15">
+        <v>9</v>
+      </c>
+      <c r="H17" s="14">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="I17" s="15">
+        <v>12</v>
+      </c>
+      <c r="J17" s="15">
+        <v>17</v>
+      </c>
+      <c r="K17" s="14">
+        <v>-29.411764705882</v>
+      </c>
+      <c r="L17" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M17" s="14">
+        <v>140</v>
+      </c>
+      <c r="N17" s="14">
         <v>100</v>
-      </c>
-      <c r="F17" s="15">
-        <v>7</v>
-      </c>
-      <c r="G17" s="15">
-        <v>5</v>
-      </c>
-      <c r="H17" s="14">
-        <v>40</v>
-      </c>
-      <c r="I17" s="15">
-        <v>10</v>
-      </c>
-      <c r="J17" s="15">
-        <v>13</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-23.076923076923</v>
-      </c>
-      <c r="L17" s="14">
-        <v>66.666666666666</v>
-      </c>
-      <c r="M17" s="14">
-        <v>100</v>
-      </c>
-      <c r="N17" s="14">
-        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
         <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="14">
-        <v>-54.545454545454</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>400</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M18" s="14">
         <v>-50</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.333333333333</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>400</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G19" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" s="14">
-        <v>-10.526315789473</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I19" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J19" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.692307692307</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L19" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M19" s="14">
-        <v>33.333333333333</v>
+        <v>21.739130434782</v>
       </c>
       <c r="N19" s="14">
-        <v>100</v>
+        <v>86.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15">
-        <v>3</v>
-      </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
         <v>3</v>
       </c>
       <c r="J20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="14">
         <v>-50</v>
       </c>
       <c r="M20" s="14">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-96</v>
+        <v>-96.739130434782</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G21" s="17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.789473684210</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J21" s="17">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K21" s="18">
-        <v>-20</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="L21" s="18">
-        <v>15.789473684210</v>
+        <v>1.923076923076</v>
       </c>
       <c r="M21" s="18">
-        <v>4.761904761904</v>
+        <v>1.923076923076</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.8</v>
+        <v>-66.025641025641</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1268,34 +1268,34 @@
         <v>5</v>
       </c>
       <c r="D24" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E24" s="14">
-        <v>-16.666666666666</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G24" s="15">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H24" s="14">
-        <v>-31.034482758620</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J24" s="15">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K24" s="14">
-        <v>-34</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="L24" s="14">
-        <v>-23.255813953488</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="M24" s="14">
-        <v>-50.746268656716</v>
+        <v>-45.070422535211</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
+        <v>100</v>
+      </c>
+      <c r="F25" s="15">
+        <v>11</v>
+      </c>
+      <c r="G25" s="15">
+        <v>11</v>
+      </c>
+      <c r="H25" s="14">
         <v>0</v>
       </c>
-      <c r="F25" s="15">
-        <v>10</v>
-      </c>
-      <c r="G25" s="15">
-        <v>15</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-33.333333333333</v>
-      </c>
       <c r="I25" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J25" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K25" s="14">
-        <v>-21.739130434782</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L25" s="14">
-        <v>12.5</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>-38.888888888888</v>
+        <v>-20</v>
       </c>
       <c r="I26" s="15">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J26" s="15">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K26" s="14">
-        <v>-34.782608695652</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="L26" s="14">
-        <v>36.363636363636</v>
+        <v>64.285714285714</v>
       </c>
       <c r="M26" s="14">
-        <v>-28.571428571428</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,29 +1431,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="D28" s="15">
         <v>1</v>
       </c>
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="15">
         <v>1</v>
       </c>
       <c r="J28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L28" s="14">
         <v>0</v>
@@ -1551,8 +1551,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1569,8 +1569,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="15">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -887,40 +887,40 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="N14" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+      <c r="J15" s="15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="14">
+        <v>100</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -939,17 +939,17 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
         <v>-100</v>
@@ -958,10 +958,10 @@
         <v>1</v>
       </c>
       <c r="J16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="L16" s="14">
         <v>-66.666666666666</v>
@@ -970,45 +970,45 @@
         <v>0</v>
       </c>
       <c r="N16" s="14">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="15">
-        <v>4</v>
-      </c>
       <c r="E17" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F17" s="15">
+        <v>5</v>
+      </c>
+      <c r="G17" s="15">
+        <v>10</v>
+      </c>
+      <c r="H17" s="14">
         <v>-50</v>
-      </c>
-      <c r="F17" s="15">
-        <v>8</v>
-      </c>
-      <c r="G17" s="15">
-        <v>9</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-11.111111111111</v>
       </c>
       <c r="I17" s="15">
         <v>12</v>
       </c>
       <c r="J17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>-29.411764705882</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L17" s="14">
-        <v>33.333333333333</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M17" s="14">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="N17" s="14">
         <v>100</v>
@@ -1018,14 +1018,14 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
@@ -1040,19 +1040,19 @@
         <v>7</v>
       </c>
       <c r="J18" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>-41.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="14">
         <v>133.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.578947368421</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,37 +1063,37 @@
         <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H19" s="14">
-        <v>-27.777777777777</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J19" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K19" s="14">
-        <v>3.703703703703</v>
+        <v>10</v>
       </c>
       <c r="L19" s="14">
         <v>0</v>
       </c>
       <c r="M19" s="14">
-        <v>21.739130434782</v>
+        <v>26.923076923076</v>
       </c>
       <c r="N19" s="14">
-        <v>86.666666666666</v>
+        <v>83.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1104,7 +1104,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
@@ -1113,19 +1113,19 @@
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I20" s="15">
         <v>3</v>
       </c>
       <c r="J20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K20" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="14">
         <v>-50</v>
@@ -1134,7 +1134,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.739130434782</v>
+        <v>-97.087378640776</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D21" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>42.857142857142</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" s="17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.571428571428</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="I21" s="17">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J21" s="17">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.516129032258</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="L21" s="18">
-        <v>1.923076923076</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="M21" s="18">
-        <v>1.923076923076</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.025641025641</v>
+        <v>-67.415730337078</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="15">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E24" s="14">
-        <v>66.666666666666</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="F24" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G24" s="15">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H24" s="14">
-        <v>-25</v>
+        <v>-37.5</v>
       </c>
       <c r="I24" s="15">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J24" s="15">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.415094339622</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="L24" s="14">
-        <v>-26.415094339622</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M24" s="14">
-        <v>-45.070422535211</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>100</v>
+        <v>-87.5</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G25" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H25" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" s="15">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K25" s="14">
-        <v>-16.666666666666</v>
+        <v>-34.375</v>
       </c>
       <c r="L25" s="14">
-        <v>-13.043478260869</v>
+        <v>-16</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>5</v>
+      </c>
+      <c r="D26" s="15">
         <v>7</v>
       </c>
-      <c r="D26" s="15">
-        <v>6</v>
-      </c>
       <c r="E26" s="14">
-        <v>16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F26" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G26" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H26" s="14">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="I26" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J26" s="15">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K26" s="14">
-        <v>-20.689655172413</v>
+        <v>-25</v>
       </c>
       <c r="L26" s="14">
-        <v>64.285714285714</v>
+        <v>42.105263157894</v>
       </c>
       <c r="M26" s="14">
-        <v>-14.814814814814</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>21</v>
+      <c r="J27" s="15">
+        <v>1</v>
+      </c>
+      <c r="K27" s="14">
+        <v>100</v>
       </c>
       <c r="L27" s="14">
         <v>-50</v>
@@ -1431,17 +1431,17 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1502,8 +1502,8 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1543,16 +1543,16 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -939,11 +939,11 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
@@ -964,13 +964,13 @@
         <v>-75</v>
       </c>
       <c r="L16" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M16" s="14">
         <v>0</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -987,31 +987,31 @@
         <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I17" s="15">
         <v>12</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K17" s="14">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="L17" s="14">
         <v>-36.842105263157</v>
-      </c>
-      <c r="L17" s="14">
-        <v>9.090909090909</v>
       </c>
       <c r="M17" s="14">
         <v>50</v>
       </c>
       <c r="N17" s="14">
-        <v>100</v>
+        <v>71.428571428571</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,7 +1022,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
@@ -1031,28 +1031,28 @@
         <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>-33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="I18" s="15">
         <v>7</v>
       </c>
       <c r="J18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="14">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L18" s="14">
         <v>133.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-53.333333333333</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.106382978723</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>46.153846153846</v>
       </c>
       <c r="I19" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J19" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K19" s="14">
-        <v>10</v>
+        <v>14.705882352941</v>
       </c>
       <c r="L19" s="14">
-        <v>0</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="M19" s="14">
-        <v>26.923076923076</v>
+        <v>50</v>
       </c>
       <c r="N19" s="14">
-        <v>83.333333333333</v>
+        <v>69.565217391304</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="15">
         <v>2</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I20" s="15">
         <v>5</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-60</v>
-      </c>
-      <c r="I20" s="15">
-        <v>3</v>
       </c>
       <c r="J20" s="15">
         <v>6</v>
       </c>
       <c r="K20" s="14">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="L20" s="14">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="M20" s="14">
         <v>-50</v>
       </c>
-      <c r="L20" s="14">
-        <v>-50</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-66.666666666666</v>
-      </c>
       <c r="N20" s="14">
-        <v>-97.087378640776</v>
+        <v>-95.726495726495</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>-58.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G21" s="17">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H21" s="18">
-        <v>-32.558139534883</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J21" s="17">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.621621621621</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.694915254237</v>
+        <v>-22.352941176470</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.694915254237</v>
+        <v>3.125</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.415730337078</v>
+        <v>-67.804878048780</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1268,34 +1268,34 @@
         <v>6</v>
       </c>
       <c r="D24" s="15">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14">
-        <v>-64.705882352941</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G24" s="15">
         <v>32</v>
       </c>
       <c r="H24" s="14">
-        <v>-37.5</v>
+        <v>-28.125</v>
       </c>
       <c r="I24" s="15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J24" s="15">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K24" s="14">
-        <v>-37.142857142857</v>
+        <v>-34.210526315789</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.137931034482</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="M24" s="14">
-        <v>-43.589743589743</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
+        <v>4</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F25" s="15">
         <v>8</v>
       </c>
-      <c r="E25" s="14">
-        <v>-87.5</v>
-      </c>
-      <c r="F25" s="15">
-        <v>9</v>
-      </c>
       <c r="G25" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J25" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K25" s="14">
-        <v>-34.375</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="L25" s="14">
-        <v>-16</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>-28.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G26" s="15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H26" s="14">
-        <v>-24</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I26" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J26" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K26" s="14">
-        <v>-25</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="L26" s="14">
-        <v>42.105263157894</v>
+        <v>31.818181818181</v>
       </c>
       <c r="M26" s="14">
-        <v>-12.903225806451</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="15">
+        <v>1</v>
       </c>
       <c r="G28" s="15">
         <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>1</v>
       </c>
       <c r="K15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>50</v>
+      </c>
+      <c r="M15" s="14">
+        <v>200</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -949,7 +949,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
         <v>-100</v>
@@ -964,10 +964,10 @@
         <v>-75</v>
       </c>
       <c r="L16" s="14">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
         <v>-90</v>
@@ -977,82 +977,82 @@
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-55.555555555555</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I17" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J17" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K17" s="14">
-        <v>-42.857142857142</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-36.842105263157</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M17" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N17" s="14">
-        <v>71.428571428571</v>
+        <v>77.777777777777</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
         <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>20</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="14">
-        <v>-53.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M18" s="14">
-        <v>-63.157894736842</v>
+        <v>-60</v>
       </c>
       <c r="N18" s="14">
-        <v>-85.106382978723</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,63 +1060,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H19" s="14">
-        <v>46.153846153846</v>
+        <v>25</v>
       </c>
       <c r="I19" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J19" s="15">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K19" s="14">
-        <v>14.705882352941</v>
+        <v>2.380952380952</v>
       </c>
       <c r="L19" s="14">
-        <v>-17.021276595744</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="M19" s="14">
-        <v>50</v>
+        <v>53.571428571428</v>
       </c>
       <c r="N19" s="14">
-        <v>69.565217391304</v>
+        <v>79.166666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
         <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15">
-        <v>4</v>
       </c>
       <c r="G20" s="15">
         <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
         <v>5</v>
@@ -1128,13 +1128,13 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="14">
         <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.726495726495</v>
+        <v>-96.124031007751</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21" s="17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="I21" s="17">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J21" s="17">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.518518518518</v>
+        <v>-18.279569892473</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.352941176470</v>
+        <v>-21.649484536082</v>
       </c>
       <c r="M21" s="18">
-        <v>3.125</v>
+        <v>10.144927536231</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.804878048780</v>
+        <v>-66.222222222222</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="15">
         <v>6</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G24" s="15">
         <v>32</v>
       </c>
       <c r="H24" s="14">
-        <v>-28.125</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="15">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J24" s="15">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K24" s="14">
-        <v>-34.210526315789</v>
+        <v>-30.487804878048</v>
       </c>
       <c r="L24" s="14">
-        <v>-25.373134328358</v>
+        <v>-27.848101265822</v>
       </c>
       <c r="M24" s="14">
-        <v>-39.024390243902</v>
+        <v>-37.362637362637</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
         <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="14">
-        <v>-50</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I25" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J25" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K25" s="14">
-        <v>-36.111111111111</v>
+        <v>-32.5</v>
       </c>
       <c r="L25" s="14">
-        <v>-14.814814814814</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H26" s="14">
-        <v>-14.285714285714</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I26" s="15">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J26" s="15">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K26" s="14">
-        <v>-25.641025641025</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L26" s="14">
-        <v>31.818181818181</v>
+        <v>44</v>
       </c>
       <c r="M26" s="14">
-        <v>-6.451612903225</v>
+        <v>2.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L27" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,11 +1431,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,23 +895,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
@@ -970,7 +970,7 @@
         <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,63 +978,63 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>500</v>
       </c>
       <c r="F17" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H17" s="14">
-        <v>-45.454545454545</v>
+        <v>25</v>
       </c>
       <c r="I17" s="15">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>-33.333333333333</v>
+        <v>-12</v>
       </c>
       <c r="L17" s="14">
-        <v>-30.434782608695</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M17" s="14">
+        <v>144.444444444444</v>
+      </c>
+      <c r="N17" s="14">
         <v>100</v>
-      </c>
-      <c r="N17" s="14">
-        <v>77.777777777777</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15">
-        <v>3</v>
-      </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="15">
         <v>8</v>
@@ -1046,13 +1046,13 @@
         <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="M18" s="14">
-        <v>-60</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.615384615384</v>
+        <v>-85.185185185185</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G19" s="15">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H19" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J19" s="15">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K19" s="14">
-        <v>2.380952380952</v>
+        <v>2.040816326530</v>
       </c>
       <c r="L19" s="14">
-        <v>-17.307692307692</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M19" s="14">
-        <v>53.571428571428</v>
+        <v>56.25</v>
       </c>
       <c r="N19" s="14">
-        <v>79.166666666666</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,11 +1103,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
@@ -1122,19 +1122,19 @@
         <v>5</v>
       </c>
       <c r="J20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L20" s="14">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M20" s="14">
         <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.124031007751</v>
+        <v>-96.428571428571</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G21" s="17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.157894736842</v>
+        <v>-10</v>
       </c>
       <c r="I21" s="17">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J21" s="17">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.279569892473</v>
+        <v>-12.745098039215</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.649484536082</v>
+        <v>-12.745098039215</v>
       </c>
       <c r="M21" s="18">
-        <v>10.144927536231</v>
+        <v>18.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.222222222222</v>
+        <v>-63.223140495867</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1268,34 +1268,34 @@
         <v>7</v>
       </c>
       <c r="D24" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G24" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H24" s="14">
-        <v>-25</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I24" s="15">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J24" s="15">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.487804878048</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.848101265822</v>
+        <v>-24.705882352941</v>
       </c>
       <c r="M24" s="14">
-        <v>-37.362637362637</v>
+        <v>-34.020618556701</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" s="14">
-        <v>-47.058823529411</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I25" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K25" s="14">
-        <v>-32.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L25" s="14">
-        <v>-18.181818181818</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G26" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H26" s="14">
-        <v>-8.695652173913</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I26" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J26" s="15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K26" s="14">
-        <v>-21.739130434782</v>
+        <v>-16</v>
       </c>
       <c r="L26" s="14">
-        <v>44</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M26" s="14">
-        <v>2.857142857142</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,23 +1387,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
@@ -1441,10 +1441,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>2</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
         <v>1</v>
       </c>
       <c r="K15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -948,11 +948,11 @@
       <c r="F16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="15">
-        <v>2</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-100</v>
+      <c r="G16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I16" s="15">
         <v>1</v>
@@ -970,7 +970,7 @@
         <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
+        <v>44.444444444444</v>
+      </c>
+      <c r="I17" s="15">
         <v>25</v>
       </c>
-      <c r="I17" s="15">
-        <v>22</v>
-      </c>
       <c r="J17" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K17" s="14">
-        <v>-12</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L17" s="14">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>144.444444444444</v>
+        <v>127.272727272727</v>
       </c>
       <c r="N17" s="14">
-        <v>100</v>
+        <v>92.307692307692</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="15">
+        <v>3</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>200</v>
       </c>
       <c r="F18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="14">
-        <v>-75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="14">
-        <v>-50</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="L18" s="14">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="M18" s="14">
-        <v>-61.904761904761</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="N18" s="14">
-        <v>-85.185185185185</v>
+        <v>-80.701754385964</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="14">
         <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J19" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K19" s="14">
-        <v>2.040816326530</v>
+        <v>5.660377358490</v>
       </c>
       <c r="L19" s="14">
-        <v>-7.407407407407</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M19" s="14">
-        <v>56.25</v>
+        <v>60</v>
       </c>
       <c r="N19" s="14">
-        <v>100</v>
+        <v>107.407407407407</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,20 +1103,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
         <v>5</v>
@@ -1134,7 +1134,7 @@
         <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.428571428571</v>
+        <v>-96.710526315789</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1145,37 +1145,37 @@
         <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>44.444444444444</v>
+        <v>62.5</v>
       </c>
       <c r="F21" s="17">
+        <v>44</v>
+      </c>
+      <c r="G21" s="17">
         <v>36</v>
       </c>
-      <c r="G21" s="17">
-        <v>40</v>
-      </c>
       <c r="H21" s="18">
-        <v>-10</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I21" s="17">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="J21" s="17">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.745098039215</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.745098039215</v>
+        <v>-4.672897196261</v>
       </c>
       <c r="M21" s="18">
-        <v>18.666666666666</v>
+        <v>24.390243902439</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.223140495867</v>
+        <v>-61.068702290076</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D24" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="F24" s="15">
+        <v>25</v>
+      </c>
+      <c r="G24" s="15">
+        <v>25</v>
+      </c>
+      <c r="H24" s="14">
         <v>0</v>
       </c>
-      <c r="F24" s="15">
-        <v>26</v>
-      </c>
-      <c r="G24" s="15">
-        <v>36</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-27.777777777777</v>
-      </c>
       <c r="I24" s="15">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J24" s="15">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.089887640449</v>
+        <v>-27.368421052631</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.705882352941</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="M24" s="14">
-        <v>-34.020618556701</v>
+        <v>-31.683168316831</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,35 +1305,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
         <v>8</v>
       </c>
       <c r="G25" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H25" s="14">
-        <v>-55.555555555555</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J25" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K25" s="14">
-        <v>-33.333333333333</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="L25" s="14">
-        <v>-28.205128205128</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="F26" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G26" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>-4.761904761904</v>
+        <v>43.75</v>
       </c>
       <c r="I26" s="15">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J26" s="15">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K26" s="14">
-        <v>-16</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="L26" s="14">
-        <v>55.555555555555</v>
+        <v>64.516129032258</v>
       </c>
       <c r="M26" s="14">
-        <v>7.692307692307</v>
+        <v>15.909090909090</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
       </c>
       <c r="K27" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L27" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,32 +895,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>100</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L15" s="14">
         <v>100</v>
@@ -928,16 +928,16 @@
       <c r="M15" s="14">
         <v>300</v>
       </c>
-      <c r="N15" s="13" t="s">
-        <v>21</v>
+      <c r="N15" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -945,8 +945,8 @@
       <c r="E16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>20</v>
+      <c r="F16" s="15">
+        <v>1</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -955,22 +955,22 @@
         <v>21</v>
       </c>
       <c r="I16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="15">
         <v>4</v>
       </c>
       <c r="K16" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L16" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.666666666666</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H17" s="14">
-        <v>44.444444444444</v>
+        <v>87.5</v>
       </c>
       <c r="I17" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" s="14">
-        <v>-10.714285714285</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M17" s="14">
-        <v>127.272727272727</v>
+        <v>125</v>
       </c>
       <c r="N17" s="14">
-        <v>92.307692307692</v>
+        <v>92.857142857142</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
         <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K18" s="14">
-        <v>-35.294117647058</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L18" s="14">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="M18" s="14">
-        <v>-52.173913043478</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.701754385964</v>
+        <v>-81.034482758620</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,48 +1060,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
         <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" s="15">
         <v>23</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I19" s="15">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J19" s="15">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K19" s="14">
-        <v>5.660377358490</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L19" s="14">
-        <v>-3.448275862068</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="M19" s="14">
-        <v>60</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N19" s="14">
-        <v>107.407407407407</v>
+        <v>85.294117647058</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>3</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1110,31 +1110,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>1</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J20" s="15">
         <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>-28.571428571428</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L20" s="14">
-        <v>-54.545454545454</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M20" s="14">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.710526315789</v>
+        <v>-95.266272189349</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
         <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="F21" s="17">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H21" s="18">
-        <v>22.222222222222</v>
+        <v>32.432432432432</v>
       </c>
       <c r="I21" s="17">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="J21" s="17">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.272727272727</v>
+        <v>-2.542372881355</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.672897196261</v>
+        <v>-4.958677685950</v>
       </c>
       <c r="M21" s="18">
-        <v>24.390243902439</v>
+        <v>27.777777777777</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.068702290076</v>
+        <v>-60.481099656357</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>3</v>
+      </c>
+      <c r="D24" s="15">
         <v>5</v>
       </c>
-      <c r="D24" s="15">
-        <v>6</v>
-      </c>
       <c r="E24" s="14">
-        <v>-16.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F24" s="15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G24" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H24" s="14">
-        <v>0</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I24" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J24" s="15">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K24" s="14">
-        <v>-27.368421052631</v>
+        <v>-28</v>
       </c>
       <c r="L24" s="14">
-        <v>-25.806451612903</v>
+        <v>-25.773195876288</v>
       </c>
       <c r="M24" s="14">
-        <v>-31.683168316831</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,35 +1305,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F25" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H25" s="14">
-        <v>-46.666666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I25" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J25" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K25" s="14">
-        <v>-38.297872340425</v>
+        <v>-34.693877551020</v>
       </c>
       <c r="L25" s="14">
-        <v>-35.555555555555</v>
+        <v>-36</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
         <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" s="14">
-        <v>43.75</v>
+        <v>73.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J26" s="15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K26" s="14">
-        <v>-1.923076923076</v>
+        <v>1.851851851851</v>
       </c>
       <c r="L26" s="14">
-        <v>64.516129032258</v>
+        <v>77.419354838709</v>
       </c>
       <c r="M26" s="14">
-        <v>15.909090909090</v>
+        <v>19.565217391304</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
         <v>-20</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>3</v>
@@ -1456,7 +1456,7 @@
         <v>-40</v>
       </c>
       <c r="L28" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1578,8 +1578,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -898,20 +898,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
@@ -936,8 +936,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,7 +946,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -955,22 +955,22 @@
         <v>21</v>
       </c>
       <c r="I16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="15">
         <v>4</v>
       </c>
       <c r="K16" s="14">
+        <v>-25</v>
+      </c>
+      <c r="L16" s="14">
         <v>-50</v>
       </c>
-      <c r="L16" s="14">
-        <v>-66.666666666666</v>
-      </c>
       <c r="M16" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.615384615384</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
         <v>8</v>
       </c>
       <c r="H17" s="14">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="I17" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K17" s="14">
-        <v>-6.896551724137</v>
+        <v>-12.5</v>
       </c>
       <c r="L17" s="14">
-        <v>-6.896551724137</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M17" s="14">
-        <v>125</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>92.857142857142</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
         <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-42.105263157894</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="M18" s="14">
-        <v>-57.692307692307</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.034482758620</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G19" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H19" s="14">
-        <v>4.347826086956</v>
+        <v>23.809523809523</v>
       </c>
       <c r="I19" s="15">
+        <v>69</v>
+      </c>
+      <c r="J19" s="15">
         <v>63</v>
       </c>
-      <c r="J19" s="15">
-        <v>57</v>
-      </c>
       <c r="K19" s="14">
-        <v>10.526315789473</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L19" s="14">
-        <v>-5.970149253731</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M19" s="14">
-        <v>61.538461538461</v>
+        <v>68.292682926829</v>
       </c>
       <c r="N19" s="14">
-        <v>85.294117647058</v>
+        <v>97.142857142857</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
       </c>
       <c r="F20" s="15">
         <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I20" s="15">
         <v>8</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-27.272727272727</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M20" s="14">
         <v>-20</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.266272189349</v>
+        <v>-95.402298850574</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="18">
-        <v>32.432432432432</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J21" s="17">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.542372881355</v>
+        <v>-1.550387596899</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.958677685950</v>
+        <v>-4.511278195488</v>
       </c>
       <c r="M21" s="18">
-        <v>27.777777777777</v>
+        <v>36.559139784946</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.481099656357</v>
+        <v>-58.631921824104</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
         <v>5</v>
       </c>
       <c r="E24" s="14">
-        <v>-40</v>
+        <v>100</v>
       </c>
       <c r="F24" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G24" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" s="14">
-        <v>-8.333333333333</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I24" s="15">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J24" s="15">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K24" s="14">
-        <v>-28</v>
+        <v>-21.904761904761</v>
       </c>
       <c r="L24" s="14">
-        <v>-25.773195876288</v>
+        <v>-21.153846153846</v>
       </c>
       <c r="M24" s="14">
-        <v>-33.333333333333</v>
+        <v>-28.695652173913</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>2</v>
+      </c>
+      <c r="D25" s="15">
         <v>3</v>
       </c>
-      <c r="D25" s="15">
-        <v>2</v>
-      </c>
       <c r="E25" s="14">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H25" s="14">
-        <v>-30.769230769230</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K25" s="14">
-        <v>-34.693877551020</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="L25" s="14">
-        <v>-36</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>7</v>
+      </c>
+      <c r="D26" s="15">
         <v>4</v>
       </c>
-      <c r="D26" s="15">
-        <v>2</v>
-      </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F26" s="15">
         <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H26" s="14">
-        <v>73.333333333333</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I26" s="15">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J26" s="15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K26" s="14">
-        <v>1.851851851851</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L26" s="14">
-        <v>77.419354838709</v>
+        <v>77.142857142857</v>
       </c>
       <c r="M26" s="14">
-        <v>19.565217391304</v>
+        <v>24</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,20 +1390,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1570,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1579,7 +1579,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,39 +905,39 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M15" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,7 +946,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -955,22 +955,22 @@
         <v>21</v>
       </c>
       <c r="I16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J16" s="15">
         <v>4</v>
       </c>
       <c r="K16" s="14">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N16" s="14">
-        <v>-78.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -980,52 +980,52 @@
       <c r="C17" s="15">
         <v>1</v>
       </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-66.666666666666</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J17" s="15">
         <v>32</v>
       </c>
       <c r="K17" s="14">
-        <v>-12.5</v>
+        <v>-9.375</v>
       </c>
       <c r="L17" s="14">
-        <v>-17.647058823529</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="M17" s="14">
-        <v>133.333333333333</v>
+        <v>141.666666666667</v>
       </c>
       <c r="N17" s="14">
-        <v>75</v>
+        <v>61.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>3</v>
-      </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>200</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
         <v>7</v>
@@ -1049,10 +1049,10 @@
         <v>200</v>
       </c>
       <c r="M18" s="14">
-        <v>-44.444444444444</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="N18" s="14">
-        <v>-76.923076923076</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H19" s="14">
-        <v>23.809523809523</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I19" s="15">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J19" s="15">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K19" s="14">
-        <v>9.523809523809</v>
+        <v>5.970149253731</v>
       </c>
       <c r="L19" s="14">
-        <v>-4.166666666666</v>
+        <v>-4.054054054054</v>
       </c>
       <c r="M19" s="14">
-        <v>68.292682926829</v>
+        <v>57.777777777777</v>
       </c>
       <c r="N19" s="14">
-        <v>97.142857142857</v>
+        <v>82.051282051282</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
+        <v>4</v>
+      </c>
+      <c r="G20" s="15">
         <v>1</v>
       </c>
-      <c r="E20" s="14">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15">
-        <v>3</v>
-      </c>
-      <c r="G20" s="15">
-        <v>2</v>
-      </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
         <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L20" s="14">
-        <v>-38.461538461538</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M20" s="14">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.402298850574</v>
+        <v>-95.187165775401</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H21" s="18">
-        <v>41.666666666666</v>
+        <v>45.161290322580</v>
       </c>
       <c r="I21" s="17">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J21" s="17">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.550387596899</v>
+        <v>0.751879699248</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.511278195488</v>
+        <v>-2.898550724637</v>
       </c>
       <c r="M21" s="18">
-        <v>36.559139784946</v>
+        <v>28.846153846153</v>
       </c>
       <c r="N21" s="18">
-        <v>-58.631921824104</v>
+        <v>-59.638554216867</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D24" s="15">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>100</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G24" s="15">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H24" s="14">
-        <v>8.695652173913</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="I24" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J24" s="15">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="K24" s="14">
-        <v>-21.904761904761</v>
+        <v>-30</v>
       </c>
       <c r="L24" s="14">
-        <v>-21.153846153846</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="M24" s="14">
-        <v>-28.695652173913</v>
+        <v>-33.858267716535</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-33.333333333333</v>
+        <v>-87.5</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H25" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I25" s="15">
+        <v>35</v>
+      </c>
+      <c r="J25" s="15">
+        <v>60</v>
+      </c>
+      <c r="K25" s="14">
         <v>-41.666666666666</v>
       </c>
-      <c r="I25" s="15">
-        <v>34</v>
-      </c>
-      <c r="J25" s="15">
-        <v>52</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-34.615384615384</v>
-      </c>
       <c r="L25" s="14">
-        <v>-34.615384615384</v>
+        <v>-38.596491228070</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
         <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>75</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G26" s="15">
         <v>12</v>
       </c>
       <c r="H26" s="14">
-        <v>116.666666666667</v>
+        <v>91.666666666666</v>
       </c>
       <c r="I26" s="15">
+        <v>65</v>
+      </c>
+      <c r="J26" s="15">
         <v>62</v>
       </c>
-      <c r="J26" s="15">
-        <v>58</v>
-      </c>
       <c r="K26" s="14">
-        <v>6.896551724137</v>
+        <v>4.838709677419</v>
       </c>
       <c r="L26" s="14">
-        <v>77.142857142857</v>
+        <v>75.675675675675</v>
       </c>
       <c r="M26" s="14">
-        <v>24</v>
+        <v>16.071428571428</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L27" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="15">
         <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -895,23 +895,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>5</v>
@@ -926,7 +926,7 @@
         <v>150</v>
       </c>
       <c r="M15" s="14">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="N15" s="14">
         <v>150</v>
@@ -936,8 +936,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -964,13 +964,13 @@
         <v>25</v>
       </c>
       <c r="L16" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="14">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="N16" s="14">
-        <v>-66.666666666666</v>
+        <v>-68.75</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D17" s="15">
+        <v>3</v>
+      </c>
+      <c r="E17" s="14">
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
         <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I17" s="15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K17" s="14">
-        <v>-9.375</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="L17" s="14">
-        <v>-19.444444444444</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>141.666666666667</v>
+        <v>153.846153846154</v>
       </c>
       <c r="N17" s="14">
-        <v>61.111111111111</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,38 +1021,38 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
         <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>75</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="M18" s="14">
-        <v>-55.882352941176</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="N18" s="14">
-        <v>-78.571428571428</v>
+        <v>-80.821917808219</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1069,31 +1069,31 @@
         <v>-50</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G19" s="15">
         <v>18</v>
       </c>
       <c r="H19" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
+        <v>72</v>
+      </c>
+      <c r="J19" s="15">
         <v>71</v>
       </c>
-      <c r="J19" s="15">
-        <v>67</v>
-      </c>
       <c r="K19" s="14">
-        <v>5.970149253731</v>
+        <v>1.408450704225</v>
       </c>
       <c r="L19" s="14">
-        <v>-4.054054054054</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M19" s="14">
-        <v>57.777777777777</v>
+        <v>53.191489361702</v>
       </c>
       <c r="N19" s="14">
-        <v>82.051282051282</v>
+        <v>56.521739130434</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,31 +1110,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
         <v>1</v>
       </c>
       <c r="H20" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="15">
         <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="L20" s="14">
-        <v>-35.714285714285</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M20" s="14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.187165775401</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1145,37 +1145,37 @@
         <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>75</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G21" s="17">
         <v>31</v>
       </c>
       <c r="H21" s="18">
-        <v>45.161290322580</v>
+        <v>25.806451612903</v>
       </c>
       <c r="I21" s="17">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J21" s="17">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K21" s="18">
-        <v>0.751879699248</v>
+        <v>-1.418439716312</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.898550724637</v>
+        <v>-2.797202797202</v>
       </c>
       <c r="M21" s="18">
-        <v>28.846153846153</v>
+        <v>24.107142857142</v>
       </c>
       <c r="N21" s="18">
-        <v>-59.638554216867</v>
+        <v>-61.388888888888</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" s="15">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E24" s="14">
-        <v>-86.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F24" s="15">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24" s="14">
-        <v>-35.483870967741</v>
+        <v>-40.625</v>
       </c>
       <c r="I24" s="15">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J24" s="15">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K24" s="14">
-        <v>-30</v>
+        <v>-31.496062992126</v>
       </c>
       <c r="L24" s="14">
-        <v>-28.205128205128</v>
+        <v>-32.03125</v>
       </c>
       <c r="M24" s="14">
-        <v>-33.858267716535</v>
+        <v>-39.160839160839</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>-87.5</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H25" s="14">
-        <v>-66.666666666666</v>
+        <v>-65</v>
       </c>
       <c r="I25" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J25" s="15">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K25" s="14">
-        <v>-41.666666666666</v>
+        <v>-46.268656716417</v>
       </c>
       <c r="L25" s="14">
-        <v>-38.596491228070</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
         <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H26" s="14">
-        <v>91.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I26" s="15">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J26" s="15">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>4.838709677419</v>
+        <v>10.606060606060</v>
       </c>
       <c r="L26" s="14">
-        <v>75.675675675675</v>
+        <v>73.809523809523</v>
       </c>
       <c r="M26" s="14">
-        <v>16.071428571428</v>
+        <v>21.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,23 +1387,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15">
-        <v>1</v>
-      </c>
-      <c r="H28" s="14">
-        <v>100</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="15">
         <v>4</v>
@@ -1551,8 +1551,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1561,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1570,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1579,7 +1579,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,31 +905,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L15" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M15" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -946,7 +946,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -964,13 +964,13 @@
         <v>25</v>
       </c>
       <c r="L16" s="14">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="M16" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N16" s="14">
-        <v>-68.75</v>
+        <v>-70.588235294117</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,13 +978,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
         <v>8</v>
@@ -996,63 +996,63 @@
         <v>14.285714285714</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J17" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K17" s="14">
-        <v>-5.714285714285</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="L17" s="14">
-        <v>-8.333333333333</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="M17" s="14">
-        <v>153.846153846154</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="L18" s="14">
-        <v>180</v>
+        <v>87.5</v>
       </c>
       <c r="M18" s="14">
-        <v>-61.111111111111</v>
+        <v>-59.459459459459</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.821917808219</v>
+        <v>-81.481481481481</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,48 +1060,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H19" s="14">
+        <v>-23.809523809523</v>
+      </c>
+      <c r="I19" s="15">
+        <v>78</v>
+      </c>
+      <c r="J19" s="15">
+        <v>78</v>
+      </c>
+      <c r="K19" s="14">
         <v>0</v>
       </c>
-      <c r="I19" s="15">
-        <v>72</v>
-      </c>
-      <c r="J19" s="15">
-        <v>71</v>
-      </c>
-      <c r="K19" s="14">
-        <v>1.408450704225</v>
-      </c>
       <c r="L19" s="14">
-        <v>-7.692307692307</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="M19" s="14">
-        <v>53.191489361702</v>
+        <v>59.183673469387</v>
       </c>
       <c r="N19" s="14">
-        <v>56.521739130434</v>
+        <v>52.941176470588</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1110,13 +1110,13 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>1</v>
       </c>
       <c r="H20" s="14">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I20" s="15">
         <v>10</v>
@@ -1131,10 +1131,10 @@
         <v>-28.571428571428</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N20" s="14">
-        <v>-95</v>
+        <v>-95.412844036697</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F21" s="17">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G21" s="17">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H21" s="18">
-        <v>25.806451612903</v>
+        <v>2.941176470588</v>
       </c>
       <c r="I21" s="17">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="J21" s="17">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.418439716312</v>
+        <v>-1.973684210526</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.797202797202</v>
+        <v>-5.095541401273</v>
       </c>
       <c r="M21" s="18">
-        <v>24.107142857142</v>
+        <v>25.210084033613</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.388888888888</v>
+        <v>-62.278481012658</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" s="14">
-        <v>-42.857142857142</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F24" s="15">
         <v>19</v>
       </c>
       <c r="G24" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H24" s="14">
-        <v>-40.625</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="I24" s="15">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J24" s="15">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K24" s="14">
-        <v>-31.496062992126</v>
+        <v>-33.823529411764</v>
       </c>
       <c r="L24" s="14">
-        <v>-32.03125</v>
+        <v>-34.306569343065</v>
       </c>
       <c r="M24" s="14">
-        <v>-39.160839160839</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-85.714285714285</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H25" s="14">
-        <v>-65</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I25" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K25" s="14">
-        <v>-46.268656716417</v>
+        <v>-46.478873239436</v>
       </c>
       <c r="L25" s="14">
-        <v>-45.454545454545</v>
+        <v>-47.945205479452</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
         <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G26" s="15">
         <v>14</v>
       </c>
       <c r="H26" s="14">
-        <v>50</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I26" s="15">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J26" s="15">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K26" s="14">
-        <v>10.606060606060</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L26" s="14">
-        <v>73.809523809523</v>
+        <v>68.888888888888</v>
       </c>
       <c r="M26" s="14">
-        <v>21.666666666666</v>
+        <v>24.590163934426</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
         <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="15">
         <v>1</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
-        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -695,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -936,8 +936,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,7 +946,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -955,22 +955,22 @@
         <v>21</v>
       </c>
       <c r="I16" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J16" s="15">
         <v>4</v>
       </c>
       <c r="K16" s="14">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L16" s="14">
-        <v>-37.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M16" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-70.588235294117</v>
+        <v>-61.111111111111</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -987,54 +987,54 @@
         <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>14.285714285714</v>
+        <v>80</v>
       </c>
       <c r="I17" s="15">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="14">
-        <v>-2.777777777777</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>-5.405405405405</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>133.333333333333</v>
+        <v>146.666666666667</v>
       </c>
       <c r="N17" s="14">
-        <v>40</v>
+        <v>27.586206896551</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>3</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="G18" s="15">
         <v>4</v>
       </c>
-      <c r="G18" s="15">
-        <v>5</v>
-      </c>
       <c r="H18" s="14">
-        <v>-20</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="15">
         <v>15</v>
@@ -1046,13 +1046,13 @@
         <v>-37.5</v>
       </c>
       <c r="L18" s="14">
-        <v>87.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-59.459459459459</v>
+        <v>-62.5</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.481481481481</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,54 +1060,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>8</v>
+      </c>
+      <c r="D19" s="15">
         <v>6</v>
       </c>
-      <c r="D19" s="15">
-        <v>7</v>
-      </c>
       <c r="E19" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F19" s="15">
+        <v>18</v>
+      </c>
+      <c r="G19" s="15">
+        <v>21</v>
+      </c>
+      <c r="H19" s="14">
         <v>-14.285714285714</v>
       </c>
-      <c r="F19" s="15">
-        <v>16</v>
-      </c>
-      <c r="G19" s="15">
-        <v>21</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-23.809523809523</v>
-      </c>
       <c r="I19" s="15">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J19" s="15">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K19" s="14">
-        <v>0</v>
+        <v>2.380952380952</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.344827586206</v>
+        <v>-9.473684210526</v>
       </c>
       <c r="M19" s="14">
-        <v>59.183673469387</v>
+        <v>75.510204081632</v>
       </c>
       <c r="N19" s="14">
-        <v>52.941176470588</v>
+        <v>50.877192982456</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
       </c>
       <c r="F20" s="15">
         <v>3</v>
@@ -1119,22 +1119,22 @@
         <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L20" s="14">
-        <v>-28.571428571428</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M20" s="14">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.412844036697</v>
+        <v>-95.319148936170</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.090909090909</v>
+        <v>62.5</v>
       </c>
       <c r="F21" s="17">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G21" s="17">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H21" s="18">
-        <v>2.941176470588</v>
+        <v>19.354838709677</v>
       </c>
       <c r="I21" s="17">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J21" s="17">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.973684210526</v>
+        <v>1.25</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.095541401273</v>
+        <v>-2.994011976047</v>
       </c>
       <c r="M21" s="18">
-        <v>25.210084033613</v>
+        <v>30.645161290322</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.278481012658</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D24" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14">
-        <v>-66.666666666666</v>
+        <v>-30</v>
       </c>
       <c r="F24" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G24" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H24" s="14">
-        <v>-47.222222222222</v>
+        <v>-60.975609756097</v>
       </c>
       <c r="I24" s="15">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J24" s="15">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="K24" s="14">
-        <v>-33.823529411764</v>
+        <v>-33.561643835616</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.306569343065</v>
+        <v>-32.167832167832</v>
       </c>
       <c r="M24" s="14">
-        <v>-42.307692307692</v>
+        <v>-42.941176470588</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H25" s="14">
-        <v>-72.727272727272</v>
+        <v>-70.833333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J25" s="15">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K25" s="14">
-        <v>-46.478873239436</v>
+        <v>-46.052631578947</v>
       </c>
       <c r="L25" s="14">
-        <v>-47.945205479452</v>
+        <v>-45.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J26" s="15">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K26" s="14">
-        <v>11.764705882352</v>
+        <v>6.756756756756</v>
       </c>
       <c r="L26" s="14">
-        <v>68.888888888888</v>
+        <v>58</v>
       </c>
       <c r="M26" s="14">
-        <v>24.590163934426</v>
+        <v>29.508196721311</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="H28" s="14">
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-123pct.xlsx
+++ b/data/source/weekly/cs-en-us-123pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="14">
+        <v>200</v>
       </c>
       <c r="I16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" s="14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L16" s="14">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M16" s="14">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N16" s="14">
-        <v>-61.111111111111</v>
+        <v>-57.894736842105</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,48 +978,48 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H17" s="14">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J17" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K17" s="14">
         <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>2.564102564102</v>
       </c>
       <c r="M17" s="14">
-        <v>146.666666666667</v>
+        <v>150</v>
       </c>
       <c r="N17" s="14">
-        <v>27.586206896551</v>
+        <v>29.032258064516</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1028,31 +1028,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="15">
         <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="15">
         <v>24</v>
       </c>
       <c r="K18" s="14">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>66.666666666666</v>
+        <v>60</v>
       </c>
       <c r="M18" s="14">
-        <v>-62.5</v>
+        <v>-60</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.333333333333</v>
+        <v>-83.505154639175</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H19" s="14">
-        <v>-14.285714285714</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I19" s="15">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J19" s="15">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K19" s="14">
-        <v>2.380952380952</v>
+        <v>1.111111111111</v>
       </c>
       <c r="L19" s="14">
-        <v>-9.473684210526</v>
+        <v>-11.650485436893</v>
       </c>
       <c r="M19" s="14">
-        <v>75.510204081632</v>
+        <v>75</v>
       </c>
       <c r="N19" s="14">
-        <v>50.877192982456</v>
+        <v>59.649122807017</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,11 +1103,11 @@
       <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>0</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>3</v>
@@ -1119,22 +1119,22 @@
         <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="15">
         <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-21.428571428571</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M20" s="14">
-        <v>-8.333333333333</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.319148936170</v>
+        <v>-95.161290322580</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" s="18">
-        <v>62.5</v>
+        <v>10</v>
       </c>
       <c r="F21" s="17">
+        <v>41</v>
+      </c>
+      <c r="G21" s="17">
         <v>37</v>
       </c>
-      <c r="G21" s="17">
-        <v>31</v>
-      </c>
       <c r="H21" s="18">
-        <v>19.354838709677</v>
+        <v>10.810810810810</v>
       </c>
       <c r="I21" s="17">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J21" s="17">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K21" s="18">
-        <v>1.25</v>
+        <v>1.764705882352</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.994011976047</v>
+        <v>-2.808988764044</v>
       </c>
       <c r="M21" s="18">
-        <v>30.645161290322</v>
+        <v>33.076923076923</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.5</v>
+        <v>-61.978021978022</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>5</v>
+      </c>
+      <c r="D24" s="15">
         <v>7</v>
       </c>
-      <c r="D24" s="15">
-        <v>10</v>
-      </c>
       <c r="E24" s="14">
-        <v>-30</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G24" s="15">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H24" s="14">
-        <v>-60.975609756097</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="I24" s="15">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J24" s="15">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K24" s="14">
-        <v>-33.561643835616</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L24" s="14">
-        <v>-32.167832167832</v>
+        <v>-31.081081081081</v>
       </c>
       <c r="M24" s="14">
-        <v>-42.941176470588</v>
+        <v>-43.956043956044</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="15">
         <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H25" s="14">
-        <v>-70.833333333333</v>
+        <v>-65</v>
       </c>
       <c r="I25" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J25" s="15">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K25" s="14">
-        <v>-46.052631578947</v>
+        <v>-47.5</v>
       </c>
       <c r="L25" s="14">
-        <v>-45.333333333333</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>-66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="15">
         <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J26" s="15">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K26" s="14">
-        <v>6.756756756756</v>
+        <v>7.792207792207</v>
       </c>
       <c r="L26" s="14">
-        <v>58</v>
+        <v>50.909090909090</v>
       </c>
       <c r="M26" s="14">
-        <v>29.508196721311</v>
+        <v>27.692307692307</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
